--- a/缺陷明细.xlsx
+++ b/缺陷明细.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="25600" windowHeight="12080" activeTab="2"/>
+    <workbookView windowWidth="25600" windowHeight="11630"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="888" uniqueCount="197">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="888" uniqueCount="193">
   <si>
     <t>登记时间</t>
   </si>
@@ -118,7 +118,7 @@
     <t>研效工具库/产品需求列表</t>
   </si>
   <si>
-    <t>New</t>
+    <t>Closed</t>
   </si>
   <si>
     <t>【导入】导入任务清单，商品名称回显异常，存在该商品-家庭宽带终端(旧机)-100000591072</t>
@@ -154,9 +154,6 @@
     <t>NL-B-171862</t>
   </si>
   <si>
-    <t>Closed</t>
-  </si>
-  <si>
     <t>【在线PPT】主商品名称过长，换行遮挡到”请描述“</t>
   </si>
   <si>
@@ -178,9 +175,6 @@
     <t>NL-B-172418</t>
   </si>
   <si>
-    <t>Fixed</t>
-  </si>
-  <si>
     <t>【在线PPT】一码_商品定价清单.xlsx样式调整，统一宋体</t>
   </si>
   <si>
@@ -226,9 +220,6 @@
     <t>NL-B-172077</t>
   </si>
   <si>
-    <t>ReOpen</t>
-  </si>
-  <si>
     <t>【在线PPT】一码_产品导出格式错误，部分数据加粗</t>
   </si>
   <si>
@@ -394,9 +385,6 @@
   </si>
   <si>
     <t>NL-B-172061</t>
-  </si>
-  <si>
-    <t>Pending</t>
   </si>
   <si>
     <t>【商品定价】销售对象用户子类型回显不正确，0是全部？</t>
@@ -1276,6 +1264,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>本周提测功能为</t>
     </r>
     <r>
@@ -1456,6 +1451,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>共计8个缺陷由基础数据引起，其中4个为产商品中心和规则中心反向数据异常引起，各中心反向数据可用性存疑，建议做端到端的反向数据同步验证。</t>
     </r>
     <r>
@@ -1519,6 +1521,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>完成场景数12/70，因涉及公共场景页面改造，自动化执行失败</t>
     </r>
     <r>
@@ -1548,6 +1557,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>测试目标：</t>
     </r>
     <r>
@@ -2821,10 +2838,10 @@
       </c>
       <c r="F3" s="14"/>
       <c r="G3" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="H3" s="14" t="s">
         <v>40</v>
-      </c>
-      <c r="H3" s="14" t="s">
-        <v>41</v>
       </c>
       <c r="I3" s="14" t="s">
         <v>30</v>
@@ -2833,7 +2850,7 @@
         <v>31</v>
       </c>
       <c r="K3" s="14" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L3" s="15">
         <v>46160.4770833333</v>
@@ -2848,10 +2865,10 @@
         <v>33</v>
       </c>
       <c r="P3" s="14" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q3" s="14" t="s">
         <v>43</v>
-      </c>
-      <c r="Q3" s="14" t="s">
-        <v>44</v>
       </c>
       <c r="R3" s="14" t="s">
         <v>34</v>
@@ -2860,10 +2877,10 @@
         <v>0</v>
       </c>
       <c r="T3" s="14" t="s">
+        <v>44</v>
+      </c>
+      <c r="U3" s="17" t="s">
         <v>45</v>
-      </c>
-      <c r="U3" s="17" t="s">
-        <v>46</v>
       </c>
       <c r="V3" s="14">
         <v>0.93</v>
@@ -2892,7 +2909,7 @@
         <v>38</v>
       </c>
       <c r="D4" s="14" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E4" s="14" t="s">
         <v>26</v>
@@ -2901,10 +2918,10 @@
         <v>27</v>
       </c>
       <c r="G4" s="14" t="s">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="H4" s="14" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="I4" s="14" t="s">
         <v>30</v>
@@ -2913,7 +2930,7 @@
         <v>31</v>
       </c>
       <c r="K4" s="14" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="L4" s="15">
         <v>46163.6888888889</v>
@@ -2926,10 +2943,10 @@
         <v>33</v>
       </c>
       <c r="P4" s="14" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="Q4" s="14" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="R4" s="14" t="s">
         <v>34</v>
@@ -2938,10 +2955,10 @@
         <v>0</v>
       </c>
       <c r="T4" s="14" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="U4" s="17" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="V4" s="14">
         <v>0.97</v>
@@ -2967,10 +2984,10 @@
         <v>23</v>
       </c>
       <c r="C5" s="13" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D5" s="14" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="E5" s="14" t="s">
         <v>26</v>
@@ -2979,13 +2996,13 @@
         <v>27</v>
       </c>
       <c r="G5" s="14" t="s">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="H5" s="14" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="I5" s="14" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="J5" s="14" t="s">
         <v>31</v>
@@ -3006,10 +3023,10 @@
         <v>33</v>
       </c>
       <c r="P5" s="14" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="Q5" s="14" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="R5" s="14" t="s">
         <v>34</v>
@@ -3050,7 +3067,7 @@
         <v>38</v>
       </c>
       <c r="D6" s="14" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="E6" s="14" t="s">
         <v>26</v>
@@ -3062,10 +3079,10 @@
         <v>28</v>
       </c>
       <c r="H6" s="14" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="I6" s="14" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="J6" s="14" t="s">
         <v>31</v>
@@ -3093,7 +3110,7 @@
         <v>35</v>
       </c>
       <c r="U6" s="14" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="V6" s="14" t="s">
         <v>37</v>
@@ -3119,10 +3136,10 @@
         <v>23</v>
       </c>
       <c r="C7" s="13" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D7" s="14" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E7" s="14" t="s">
         <v>26</v>
@@ -3131,13 +3148,13 @@
         <v>27</v>
       </c>
       <c r="G7" s="14" t="s">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="H7" s="14" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="I7" s="14" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="J7" s="14" t="s">
         <v>31</v>
@@ -3158,10 +3175,10 @@
         <v>33</v>
       </c>
       <c r="P7" s="14" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="Q7" s="14" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="R7" s="14" t="s">
         <v>34</v>
@@ -3202,7 +3219,7 @@
         <v>38</v>
       </c>
       <c r="D8" s="14" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E8" s="14" t="s">
         <v>26</v>
@@ -3211,10 +3228,10 @@
         <v>27</v>
       </c>
       <c r="G8" s="14" t="s">
-        <v>64</v>
+        <v>28</v>
       </c>
       <c r="H8" s="14" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="I8" s="14" t="s">
         <v>30</v>
@@ -3223,7 +3240,7 @@
         <v>31</v>
       </c>
       <c r="K8" s="14" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="L8" s="15">
         <v>46161.6576388889</v>
@@ -3236,10 +3253,10 @@
         <v>33</v>
       </c>
       <c r="P8" s="14" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="Q8" s="14" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="R8" s="14" t="s">
         <v>34</v>
@@ -3248,10 +3265,10 @@
         <v>1</v>
       </c>
       <c r="T8" s="14" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="U8" s="17" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="V8" s="14">
         <v>2.04</v>
@@ -3280,7 +3297,7 @@
         <v>24</v>
       </c>
       <c r="D9" s="14" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="E9" s="14" t="s">
         <v>26</v>
@@ -3289,13 +3306,13 @@
         <v>27</v>
       </c>
       <c r="G9" s="14" t="s">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="H9" s="14" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="I9" s="14" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="J9" s="14" t="s">
         <v>31</v>
@@ -3314,10 +3331,10 @@
         <v>33</v>
       </c>
       <c r="P9" s="14" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="Q9" s="14" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="R9" s="14" t="s">
         <v>34</v>
@@ -3358,7 +3375,7 @@
         <v>38</v>
       </c>
       <c r="D10" s="14" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="E10" s="14" t="s">
         <v>26</v>
@@ -3370,7 +3387,7 @@
         <v>28</v>
       </c>
       <c r="H10" s="14" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="I10" s="14" t="s">
         <v>30</v>
@@ -3379,7 +3396,7 @@
         <v>31</v>
       </c>
       <c r="K10" s="14" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L10" s="15">
         <v>46163.48125</v>
@@ -3401,7 +3418,7 @@
         <v>35</v>
       </c>
       <c r="U10" s="14" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="V10" s="14" t="s">
         <v>37</v>
@@ -3430,7 +3447,7 @@
         <v>38</v>
       </c>
       <c r="D11" s="14" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="E11" s="14" t="s">
         <v>26</v>
@@ -3439,10 +3456,10 @@
         <v>27</v>
       </c>
       <c r="G11" s="14" t="s">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="H11" s="14" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="I11" s="14" t="s">
         <v>30</v>
@@ -3451,7 +3468,7 @@
         <v>31</v>
       </c>
       <c r="K11" s="14" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L11" s="15">
         <v>46161.4722222222</v>
@@ -3466,10 +3483,10 @@
         <v>33</v>
       </c>
       <c r="P11" s="14" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="Q11" s="14" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="R11" s="14" t="s">
         <v>34</v>
@@ -3510,17 +3527,17 @@
         <v>38</v>
       </c>
       <c r="D12" s="14" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="E12" s="14" t="s">
         <v>26</v>
       </c>
       <c r="F12" s="14"/>
       <c r="G12" s="14" t="s">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="H12" s="14" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="I12" s="14" t="s">
         <v>30</v>
@@ -3529,7 +3546,7 @@
         <v>31</v>
       </c>
       <c r="K12" s="14" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L12" s="15">
         <v>46160.6986111111</v>
@@ -3544,10 +3561,10 @@
         <v>33</v>
       </c>
       <c r="P12" s="14" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q12" s="14" t="s">
         <v>43</v>
-      </c>
-      <c r="Q12" s="14" t="s">
-        <v>44</v>
       </c>
       <c r="R12" s="14" t="s">
         <v>34</v>
@@ -3588,7 +3605,7 @@
         <v>38</v>
       </c>
       <c r="D13" s="14" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="E13" s="14" t="s">
         <v>26</v>
@@ -3600,7 +3617,7 @@
         <v>28</v>
       </c>
       <c r="H13" s="14" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="I13" s="14" t="s">
         <v>30</v>
@@ -3609,7 +3626,7 @@
         <v>31</v>
       </c>
       <c r="K13" s="14" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L13" s="15">
         <v>46161.6680555556</v>
@@ -3628,10 +3645,10 @@
         <v>0</v>
       </c>
       <c r="T13" s="14" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="U13" s="14" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="V13" s="14" t="s">
         <v>37</v>
@@ -3660,7 +3677,7 @@
         <v>38</v>
       </c>
       <c r="D14" s="14" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="E14" s="14" t="s">
         <v>26</v>
@@ -3672,7 +3689,7 @@
         <v>28</v>
       </c>
       <c r="H14" s="14" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="I14" s="14" t="s">
         <v>30</v>
@@ -3681,7 +3698,7 @@
         <v>31</v>
       </c>
       <c r="K14" s="14" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="L14" s="15">
         <v>46161.4375</v>
@@ -3732,7 +3749,7 @@
         <v>38</v>
       </c>
       <c r="D15" s="14" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="E15" s="14" t="s">
         <v>26</v>
@@ -3741,10 +3758,10 @@
         <v>27</v>
       </c>
       <c r="G15" s="14" t="s">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="H15" s="14" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="I15" s="14" t="s">
         <v>30</v>
@@ -3753,7 +3770,7 @@
         <v>31</v>
       </c>
       <c r="K15" s="14" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L15" s="15">
         <v>46161.6506944444</v>
@@ -3768,10 +3785,10 @@
         <v>33</v>
       </c>
       <c r="P15" s="14" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q15" s="14" t="s">
         <v>43</v>
-      </c>
-      <c r="Q15" s="14" t="s">
-        <v>44</v>
       </c>
       <c r="R15" s="14" t="s">
         <v>34</v>
@@ -3783,7 +3800,7 @@
         <v>35</v>
       </c>
       <c r="U15" s="17" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="V15" s="14">
         <v>0.06</v>
@@ -3809,20 +3826,20 @@
         <v>23</v>
       </c>
       <c r="C16" s="13" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D16" s="14" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="E16" s="14" t="s">
         <v>26</v>
       </c>
       <c r="F16" s="14"/>
       <c r="G16" s="14" t="s">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="H16" s="14" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="I16" s="14" t="s">
         <v>30</v>
@@ -3846,10 +3863,10 @@
         <v>33</v>
       </c>
       <c r="P16" s="14" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="Q16" s="14" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="R16" s="14" t="s">
         <v>34</v>
@@ -3887,10 +3904,10 @@
         <v>23</v>
       </c>
       <c r="C17" s="13" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D17" s="14" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="E17" s="14" t="s">
         <v>26</v>
@@ -3899,10 +3916,10 @@
         <v>27</v>
       </c>
       <c r="G17" s="14" t="s">
-        <v>64</v>
+        <v>28</v>
       </c>
       <c r="H17" s="14" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="I17" s="14" t="s">
         <v>30</v>
@@ -3911,7 +3928,7 @@
         <v>31</v>
       </c>
       <c r="K17" s="14" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L17" s="15">
         <v>46161.4465277778</v>
@@ -3924,10 +3941,10 @@
         <v>33</v>
       </c>
       <c r="P17" s="14" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="Q17" s="14" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="R17" s="14" t="s">
         <v>34</v>
@@ -3939,7 +3956,7 @@
         <v>35</v>
       </c>
       <c r="U17" s="17" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="V17" s="14">
         <v>3.03</v>
@@ -3968,7 +3985,7 @@
         <v>38</v>
       </c>
       <c r="D18" s="14" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="E18" s="14" t="s">
         <v>26</v>
@@ -3977,10 +3994,10 @@
         <v>27</v>
       </c>
       <c r="G18" s="14" t="s">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="H18" s="14" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="I18" s="14" t="s">
         <v>30</v>
@@ -3989,7 +4006,7 @@
         <v>31</v>
       </c>
       <c r="K18" s="14" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="L18" s="15">
         <v>46161.4986111111</v>
@@ -4004,10 +4021,10 @@
         <v>33</v>
       </c>
       <c r="P18" s="14" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="Q18" s="14" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="R18" s="14" t="s">
         <v>34</v>
@@ -4048,7 +4065,7 @@
         <v>38</v>
       </c>
       <c r="D19" s="14" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="E19" s="14" t="s">
         <v>26</v>
@@ -4057,10 +4074,10 @@
         <v>27</v>
       </c>
       <c r="G19" s="14" t="s">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="H19" s="14" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="I19" s="14" t="s">
         <v>30</v>
@@ -4069,7 +4086,7 @@
         <v>31</v>
       </c>
       <c r="K19" s="14" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L19" s="15">
         <v>46161.6388888889</v>
@@ -4084,10 +4101,10 @@
         <v>33</v>
       </c>
       <c r="P19" s="14" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="Q19" s="14" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="R19" s="14" t="s">
         <v>34</v>
@@ -4099,7 +4116,7 @@
         <v>35</v>
       </c>
       <c r="U19" s="17" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="V19" s="14">
         <v>2.73</v>
@@ -4128,7 +4145,7 @@
         <v>38</v>
       </c>
       <c r="D20" s="14" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="E20" s="14" t="s">
         <v>26</v>
@@ -4137,10 +4154,10 @@
         <v>27</v>
       </c>
       <c r="G20" s="14" t="s">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="H20" s="14" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="I20" s="14" t="s">
         <v>30</v>
@@ -4149,7 +4166,7 @@
         <v>31</v>
       </c>
       <c r="K20" s="14" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L20" s="15">
         <v>46161.4409722222</v>
@@ -4164,10 +4181,10 @@
         <v>33</v>
       </c>
       <c r="P20" s="14" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="Q20" s="14" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="R20" s="14" t="s">
         <v>34</v>
@@ -4208,7 +4225,7 @@
         <v>38</v>
       </c>
       <c r="D21" s="14" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="E21" s="14" t="s">
         <v>26</v>
@@ -4217,10 +4234,10 @@
         <v>27</v>
       </c>
       <c r="G21" s="14" t="s">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="H21" s="14" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="I21" s="14" t="s">
         <v>30</v>
@@ -4229,7 +4246,7 @@
         <v>31</v>
       </c>
       <c r="K21" s="14" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="L21" s="15">
         <v>46161.7291666667</v>
@@ -4239,13 +4256,13 @@
       </c>
       <c r="N21" s="14"/>
       <c r="O21" s="14" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="P21" s="14" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="Q21" s="14" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="R21" s="14" t="s">
         <v>34</v>
@@ -4257,7 +4274,7 @@
         <v>35</v>
       </c>
       <c r="U21" s="17" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="V21" s="14">
         <v>2.89</v>
@@ -4286,17 +4303,17 @@
         <v>38</v>
       </c>
       <c r="D22" s="14" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="E22" s="14" t="s">
         <v>26</v>
       </c>
       <c r="F22" s="14"/>
       <c r="G22" s="14" t="s">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="H22" s="14" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="I22" s="14" t="s">
         <v>30</v>
@@ -4305,7 +4322,7 @@
         <v>31</v>
       </c>
       <c r="K22" s="14" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L22" s="15">
         <v>46160.4722222222</v>
@@ -4320,10 +4337,10 @@
         <v>33</v>
       </c>
       <c r="P22" s="14" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q22" s="14" t="s">
         <v>43</v>
-      </c>
-      <c r="Q22" s="14" t="s">
-        <v>44</v>
       </c>
       <c r="R22" s="14" t="s">
         <v>34</v>
@@ -4335,7 +4352,7 @@
         <v>35</v>
       </c>
       <c r="U22" s="17" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="V22" s="14">
         <v>0.93</v>
@@ -4364,7 +4381,7 @@
         <v>38</v>
       </c>
       <c r="D23" s="14" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="E23" s="14" t="s">
         <v>26</v>
@@ -4373,10 +4390,10 @@
         <v>27</v>
       </c>
       <c r="G23" s="14" t="s">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="H23" s="14" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="I23" s="14" t="s">
         <v>30</v>
@@ -4385,7 +4402,7 @@
         <v>31</v>
       </c>
       <c r="K23" s="14" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L23" s="15">
         <v>46161.4361111111</v>
@@ -4398,10 +4415,10 @@
         <v>33</v>
       </c>
       <c r="P23" s="14" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="Q23" s="14" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="R23" s="14" t="s">
         <v>34</v>
@@ -4410,10 +4427,10 @@
         <v>0</v>
       </c>
       <c r="T23" s="14" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="U23" s="17" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="V23" s="14">
         <v>3.03</v>
@@ -4442,7 +4459,7 @@
         <v>38</v>
       </c>
       <c r="D24" s="14" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="E24" s="14" t="s">
         <v>26</v>
@@ -4451,10 +4468,10 @@
         <v>27</v>
       </c>
       <c r="G24" s="14" t="s">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="H24" s="14" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="I24" s="14" t="s">
         <v>30</v>
@@ -4478,10 +4495,10 @@
         <v>33</v>
       </c>
       <c r="P24" s="14" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="Q24" s="14" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="R24" s="14" t="s">
         <v>34</v>
@@ -4519,10 +4536,10 @@
         <v>23</v>
       </c>
       <c r="C25" s="13" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D25" s="14" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="E25" s="14" t="s">
         <v>26</v>
@@ -4531,19 +4548,19 @@
         <v>27</v>
       </c>
       <c r="G25" s="14" t="s">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="H25" s="14" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="I25" s="14" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="J25" s="14" t="s">
         <v>31</v>
       </c>
       <c r="K25" s="14" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="L25" s="15">
         <v>46161.4173611111</v>
@@ -4558,10 +4575,10 @@
         <v>33</v>
       </c>
       <c r="P25" s="14" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="Q25" s="14" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="R25" s="14" t="s">
         <v>34</v>
@@ -4570,10 +4587,10 @@
         <v>0</v>
       </c>
       <c r="T25" s="14" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="U25" s="17" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="V25" s="14">
         <v>0.27</v>
@@ -4599,10 +4616,10 @@
         <v>23</v>
       </c>
       <c r="C26" s="13" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D26" s="14" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="E26" s="14" t="s">
         <v>26</v>
@@ -4611,10 +4628,10 @@
         <v>27</v>
       </c>
       <c r="G26" s="14" t="s">
-        <v>115</v>
+        <v>28</v>
       </c>
       <c r="H26" s="14" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="I26" s="14" t="s">
         <v>30</v>
@@ -4623,7 +4640,7 @@
         <v>31</v>
       </c>
       <c r="K26" s="14" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="L26" s="15">
         <v>46161.625</v>
@@ -4671,10 +4688,10 @@
         <v>23</v>
       </c>
       <c r="C27" s="13" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D27" s="14" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="E27" s="14" t="s">
         <v>26</v>
@@ -4683,10 +4700,10 @@
         <v>27</v>
       </c>
       <c r="G27" s="14" t="s">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="H27" s="14" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="I27" s="14" t="s">
         <v>30</v>
@@ -4710,10 +4727,10 @@
         <v>33</v>
       </c>
       <c r="P27" s="14" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="Q27" s="14" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="R27" s="14" t="s">
         <v>34</v>
@@ -4722,7 +4739,7 @@
         <v>0</v>
       </c>
       <c r="T27" s="14" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="U27" s="14" t="s">
         <v>36</v>
@@ -4754,7 +4771,7 @@
         <v>38</v>
       </c>
       <c r="D28" s="14" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="E28" s="14" t="s">
         <v>26</v>
@@ -4766,7 +4783,7 @@
         <v>28</v>
       </c>
       <c r="H28" s="14" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="I28" s="14" t="s">
         <v>30</v>
@@ -4775,7 +4792,7 @@
         <v>31</v>
       </c>
       <c r="K28" s="14" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L28" s="15">
         <v>46161.4652777778</v>
@@ -4794,10 +4811,10 @@
         <v>0</v>
       </c>
       <c r="T28" s="14" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="U28" s="14" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="V28" s="14" t="s">
         <v>37</v>
@@ -4826,7 +4843,7 @@
         <v>38</v>
       </c>
       <c r="D29" s="14" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="E29" s="14" t="s">
         <v>26</v>
@@ -4835,10 +4852,10 @@
         <v>27</v>
       </c>
       <c r="G29" s="14" t="s">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="H29" s="14" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="I29" s="14" t="s">
         <v>30</v>
@@ -4847,7 +4864,7 @@
         <v>31</v>
       </c>
       <c r="K29" s="14" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L29" s="15">
         <v>46161.4416666667</v>
@@ -4862,10 +4879,10 @@
         <v>33</v>
       </c>
       <c r="P29" s="14" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="Q29" s="14" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="R29" s="14" t="s">
         <v>34</v>
@@ -4903,22 +4920,22 @@
         <v>23</v>
       </c>
       <c r="C30" s="13" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D30" s="14" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="E30" s="14" t="s">
         <v>26</v>
       </c>
       <c r="F30" s="14" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="G30" s="14" t="s">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="H30" s="14" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="I30" s="14" t="s">
         <v>30</v>
@@ -4942,10 +4959,10 @@
         <v>33</v>
       </c>
       <c r="P30" s="14" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="Q30" s="14" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="R30" s="14" t="s">
         <v>34</v>
@@ -4983,10 +5000,10 @@
         <v>23</v>
       </c>
       <c r="C31" s="13" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D31" s="14" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="E31" s="14" t="s">
         <v>26</v>
@@ -4995,10 +5012,10 @@
         <v>27</v>
       </c>
       <c r="G31" s="14" t="s">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="H31" s="14" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="I31" s="14" t="s">
         <v>30</v>
@@ -5007,7 +5024,7 @@
         <v>31</v>
       </c>
       <c r="K31" s="14" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="L31" s="15">
         <v>46163.4784722222</v>
@@ -5020,10 +5037,10 @@
         <v>33</v>
       </c>
       <c r="P31" s="14" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="Q31" s="14" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="R31" s="14" t="s">
         <v>34</v>
@@ -5035,7 +5052,7 @@
         <v>35</v>
       </c>
       <c r="U31" s="17" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="V31" s="14">
         <v>0.96</v>
@@ -5061,10 +5078,10 @@
         <v>23</v>
       </c>
       <c r="C32" s="13" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D32" s="14" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="E32" s="14" t="s">
         <v>26</v>
@@ -5076,7 +5093,7 @@
         <v>28</v>
       </c>
       <c r="H32" s="14" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="I32" s="14" t="s">
         <v>30</v>
@@ -5107,7 +5124,7 @@
         <v>35</v>
       </c>
       <c r="U32" s="14" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="V32" s="14" t="s">
         <v>37</v>
@@ -5133,10 +5150,10 @@
         <v>23</v>
       </c>
       <c r="C33" s="13" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="D33" s="14" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="E33" s="14" t="s">
         <v>26</v>
@@ -5145,10 +5162,10 @@
         <v>27</v>
       </c>
       <c r="G33" s="14" t="s">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="H33" s="14" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="I33" s="14" t="s">
         <v>30</v>
@@ -5157,7 +5174,7 @@
         <v>31</v>
       </c>
       <c r="K33" s="14" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="L33" s="15">
         <v>46164.4680555556</v>
@@ -5170,10 +5187,10 @@
         <v>33</v>
       </c>
       <c r="P33" s="14" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="Q33" s="14" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="R33" s="14" t="s">
         <v>34</v>
@@ -5182,10 +5199,10 @@
         <v>0</v>
       </c>
       <c r="T33" s="14" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="U33" s="14" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="V33" s="14">
         <v>0.04</v>
@@ -5211,10 +5228,10 @@
         <v>23</v>
       </c>
       <c r="C34" s="13" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D34" s="14" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="E34" s="14" t="s">
         <v>26</v>
@@ -5226,7 +5243,7 @@
         <v>28</v>
       </c>
       <c r="H34" s="14" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="I34" s="14" t="s">
         <v>30</v>
@@ -5235,7 +5252,7 @@
         <v>31</v>
       </c>
       <c r="K34" s="14" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L34" s="15">
         <v>46160.7090277778</v>
@@ -5254,10 +5271,10 @@
         <v>0</v>
       </c>
       <c r="T34" s="14" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="U34" s="14" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="V34" s="14" t="s">
         <v>37</v>
@@ -5286,7 +5303,7 @@
         <v>38</v>
       </c>
       <c r="D35" s="14" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="E35" s="14" t="s">
         <v>26</v>
@@ -5295,10 +5312,10 @@
         <v>27</v>
       </c>
       <c r="G35" s="14" t="s">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="H35" s="14" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="I35" s="14" t="s">
         <v>30</v>
@@ -5320,10 +5337,10 @@
         <v>33</v>
       </c>
       <c r="P35" s="14" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="Q35" s="14" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="R35" s="14" t="s">
         <v>34</v>
@@ -5332,10 +5349,10 @@
         <v>0</v>
       </c>
       <c r="T35" s="14" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="U35" s="17" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="V35" s="14">
         <v>1.93</v>
@@ -5361,10 +5378,10 @@
         <v>23</v>
       </c>
       <c r="C36" s="13" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D36" s="14" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="E36" s="14" t="s">
         <v>26</v>
@@ -5373,10 +5390,10 @@
         <v>27</v>
       </c>
       <c r="G36" s="14" t="s">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="H36" s="14" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="I36" s="14" t="s">
         <v>30</v>
@@ -5400,10 +5417,10 @@
         <v>33</v>
       </c>
       <c r="P36" s="14" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="Q36" s="14" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="R36" s="14" t="s">
         <v>34</v>
@@ -5441,10 +5458,10 @@
         <v>23</v>
       </c>
       <c r="C37" s="13" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="D37" s="14" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="E37" s="14" t="s">
         <v>26</v>
@@ -5453,10 +5470,10 @@
         <v>27</v>
       </c>
       <c r="G37" s="14" t="s">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="H37" s="14" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="I37" s="14" t="s">
         <v>30</v>
@@ -5465,7 +5482,7 @@
         <v>31</v>
       </c>
       <c r="K37" s="14" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="L37" s="15">
         <v>46164.4680555556</v>
@@ -5478,10 +5495,10 @@
         <v>33</v>
       </c>
       <c r="P37" s="14" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="Q37" s="14" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="R37" s="14" t="s">
         <v>34</v>
@@ -5490,10 +5507,10 @@
         <v>0</v>
       </c>
       <c r="T37" s="14" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="U37" s="17" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="V37" s="14">
         <v>0.04</v>
@@ -5519,20 +5536,20 @@
         <v>23</v>
       </c>
       <c r="C38" s="13" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D38" s="14" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="E38" s="14" t="s">
         <v>26</v>
       </c>
       <c r="F38" s="14"/>
       <c r="G38" s="14" t="s">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="H38" s="14" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="I38" s="14" t="s">
         <v>30</v>
@@ -5541,7 +5558,7 @@
         <v>31</v>
       </c>
       <c r="K38" s="14" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="L38" s="15">
         <v>46160.4520833333</v>
@@ -5556,10 +5573,10 @@
         <v>33</v>
       </c>
       <c r="P38" s="14" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="Q38" s="14" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="R38" s="14" t="s">
         <v>34</v>
@@ -5571,7 +5588,7 @@
         <v>35</v>
       </c>
       <c r="U38" s="17" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="V38" s="14">
         <v>0.91</v>
@@ -5597,20 +5614,20 @@
         <v>23</v>
       </c>
       <c r="C39" s="13" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D39" s="14" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="E39" s="14" t="s">
         <v>26</v>
       </c>
       <c r="F39" s="14"/>
       <c r="G39" s="14" t="s">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="H39" s="14" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="I39" s="14" t="s">
         <v>30</v>
@@ -5619,7 +5636,7 @@
         <v>31</v>
       </c>
       <c r="K39" s="14" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="L39" s="15">
         <v>46160.3743055556</v>
@@ -5634,10 +5651,10 @@
         <v>33</v>
       </c>
       <c r="P39" s="14" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="Q39" s="14" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="R39" s="14" t="s">
         <v>34</v>
@@ -5649,7 +5666,7 @@
         <v>35</v>
       </c>
       <c r="U39" s="17" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="V39" s="14">
         <v>0.25</v>
@@ -5678,7 +5695,7 @@
         <v>38</v>
       </c>
       <c r="D40" s="14" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="E40" s="14" t="s">
         <v>26</v>
@@ -5690,7 +5707,7 @@
         <v>28</v>
       </c>
       <c r="H40" s="14" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="I40" s="14" t="s">
         <v>30</v>
@@ -5699,7 +5716,7 @@
         <v>31</v>
       </c>
       <c r="K40" s="14" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L40" s="15">
         <v>46161.6520833333</v>
@@ -5721,7 +5738,7 @@
         <v>35</v>
       </c>
       <c r="U40" s="14" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="V40" s="14" t="s">
         <v>37</v>
@@ -5750,7 +5767,7 @@
         <v>38</v>
       </c>
       <c r="D41" s="14" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="E41" s="14" t="s">
         <v>26</v>
@@ -5759,10 +5776,10 @@
         <v>27</v>
       </c>
       <c r="G41" s="14" t="s">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="H41" s="14" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="I41" s="14" t="s">
         <v>30</v>
@@ -5771,7 +5788,7 @@
         <v>31</v>
       </c>
       <c r="K41" s="14" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="L41" s="15">
         <v>46161.6541666667</v>
@@ -5786,10 +5803,10 @@
         <v>33</v>
       </c>
       <c r="P41" s="14" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="Q41" s="14" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="R41" s="14" t="s">
         <v>34</v>
@@ -5798,10 +5815,10 @@
         <v>0</v>
       </c>
       <c r="T41" s="14" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="U41" s="14" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="V41" s="14">
         <v>0.94</v>
@@ -5827,10 +5844,10 @@
         <v>23</v>
       </c>
       <c r="C42" s="13" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="D42" s="14" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="E42" s="14" t="s">
         <v>26</v>
@@ -5842,7 +5859,7 @@
         <v>28</v>
       </c>
       <c r="H42" s="14" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="I42" s="14" t="s">
         <v>30</v>
@@ -5851,7 +5868,7 @@
         <v>31</v>
       </c>
       <c r="K42" s="14" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="L42" s="15">
         <v>46164.6722222222</v>
@@ -5873,7 +5890,7 @@
         <v>35</v>
       </c>
       <c r="U42" s="14" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="V42" s="14" t="s">
         <v>37</v>
@@ -5902,7 +5919,7 @@
         <v>38</v>
       </c>
       <c r="D43" s="14" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="E43" s="14" t="s">
         <v>26</v>
@@ -5911,10 +5928,10 @@
         <v>27</v>
       </c>
       <c r="G43" s="14" t="s">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="H43" s="14" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="I43" s="14" t="s">
         <v>30</v>
@@ -5923,7 +5940,7 @@
         <v>31</v>
       </c>
       <c r="K43" s="14" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L43" s="15">
         <v>46160.6027777778</v>
@@ -5938,10 +5955,10 @@
         <v>33</v>
       </c>
       <c r="P43" s="14" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="Q43" s="14" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="R43" s="14" t="s">
         <v>34</v>
@@ -5982,7 +5999,7 @@
         <v>38</v>
       </c>
       <c r="D44" s="14" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="E44" s="14" t="s">
         <v>26</v>
@@ -5994,7 +6011,7 @@
         <v>28</v>
       </c>
       <c r="H44" s="14" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="I44" s="14" t="s">
         <v>30</v>
@@ -6003,7 +6020,7 @@
         <v>31</v>
       </c>
       <c r="K44" s="14" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L44" s="15">
         <v>46163.66875</v>
@@ -6022,10 +6039,10 @@
         <v>0</v>
       </c>
       <c r="T44" s="14" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="U44" s="14" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="V44" s="14" t="s">
         <v>37</v>
@@ -6054,7 +6071,7 @@
         <v>38</v>
       </c>
       <c r="D45" s="14" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="E45" s="14" t="s">
         <v>26</v>
@@ -6066,16 +6083,16 @@
         <v>28</v>
       </c>
       <c r="H45" s="14" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="I45" s="14" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="J45" s="14" t="s">
         <v>31</v>
       </c>
       <c r="K45" s="14" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L45" s="15">
         <v>46161.46875</v>
@@ -6126,7 +6143,7 @@
         <v>38</v>
       </c>
       <c r="D46" s="14" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="E46" s="14" t="s">
         <v>26</v>
@@ -6135,10 +6152,10 @@
         <v>27</v>
       </c>
       <c r="G46" s="14" t="s">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="H46" s="14" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="I46" s="14" t="s">
         <v>30</v>
@@ -6147,7 +6164,7 @@
         <v>31</v>
       </c>
       <c r="K46" s="14" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L46" s="15">
         <v>46161.6770833333</v>
@@ -6162,10 +6179,10 @@
         <v>33</v>
       </c>
       <c r="P46" s="14" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="Q46" s="14" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="R46" s="14" t="s">
         <v>34</v>
@@ -6174,10 +6191,10 @@
         <v>0</v>
       </c>
       <c r="T46" s="14" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="U46" s="17" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="V46" s="14">
         <v>0.03</v>
@@ -6206,7 +6223,7 @@
         <v>38</v>
       </c>
       <c r="D47" s="14" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="E47" s="14" t="s">
         <v>26</v>
@@ -6215,10 +6232,10 @@
         <v>27</v>
       </c>
       <c r="G47" s="14" t="s">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="H47" s="14" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="I47" s="14" t="s">
         <v>30</v>
@@ -6227,7 +6244,7 @@
         <v>31</v>
       </c>
       <c r="K47" s="14" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L47" s="15">
         <v>46161.6409722222</v>
@@ -6242,10 +6259,10 @@
         <v>33</v>
       </c>
       <c r="P47" s="14" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="Q47" s="14" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="R47" s="14" t="s">
         <v>34</v>
@@ -6257,7 +6274,7 @@
         <v>35</v>
       </c>
       <c r="U47" s="17" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="V47" s="14">
         <v>2.73</v>
@@ -6286,7 +6303,7 @@
         <v>38</v>
       </c>
       <c r="D48" s="14" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="E48" s="14" t="s">
         <v>26</v>
@@ -6295,10 +6312,10 @@
         <v>27</v>
       </c>
       <c r="G48" s="14" t="s">
-        <v>115</v>
+        <v>28</v>
       </c>
       <c r="H48" s="14" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="I48" s="14" t="s">
         <v>30</v>
@@ -6307,7 +6324,7 @@
         <v>31</v>
       </c>
       <c r="K48" s="14" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="L48" s="15">
         <v>46161.6527777778</v>
@@ -6329,7 +6346,7 @@
         <v>35</v>
       </c>
       <c r="U48" s="14" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="V48" s="14" t="s">
         <v>37</v>
@@ -6355,10 +6372,10 @@
         <v>23</v>
       </c>
       <c r="C49" s="13" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D49" s="14" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="E49" s="14" t="s">
         <v>26</v>
@@ -6367,10 +6384,10 @@
         <v>27</v>
       </c>
       <c r="G49" s="14" t="s">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="H49" s="14" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="I49" s="14" t="s">
         <v>30</v>
@@ -6379,7 +6396,7 @@
         <v>31</v>
       </c>
       <c r="K49" s="14" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L49" s="15">
         <v>46160.7069444444</v>
@@ -6394,10 +6411,10 @@
         <v>33</v>
       </c>
       <c r="P49" s="14" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="Q49" s="14" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="R49" s="14" t="s">
         <v>34</v>
@@ -6406,10 +6423,10 @@
         <v>0</v>
       </c>
       <c r="T49" s="14" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="U49" s="14" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="V49" s="14">
         <v>2.02</v>
@@ -6451,43 +6468,43 @@
   <sheetData>
     <row r="1" spans="1:13">
       <c r="A1" s="5" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="C1" s="5" t="s">
         <v>1</v>
       </c>
       <c r="D1" s="5" t="s">
+        <v>168</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>169</v>
+      </c>
+      <c r="F1" s="5" t="s">
+        <v>170</v>
+      </c>
+      <c r="G1" s="5" t="s">
+        <v>171</v>
+      </c>
+      <c r="H1" s="5" t="s">
         <v>172</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="I1" s="5" t="s">
         <v>173</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="J1" s="5" t="s">
         <v>174</v>
       </c>
-      <c r="G1" s="5" t="s">
+      <c r="K1" s="5" t="s">
         <v>175</v>
       </c>
-      <c r="H1" s="5" t="s">
+      <c r="L1" s="6" t="s">
         <v>176</v>
       </c>
-      <c r="I1" s="5" t="s">
+      <c r="M1" s="5" t="s">
         <v>177</v>
-      </c>
-      <c r="J1" s="5" t="s">
-        <v>178</v>
-      </c>
-      <c r="K1" s="5" t="s">
-        <v>179</v>
-      </c>
-      <c r="L1" s="6" t="s">
-        <v>180</v>
-      </c>
-      <c r="M1" s="5" t="s">
-        <v>181</v>
       </c>
     </row>
     <row r="2" spans="1:13">
@@ -6528,7 +6545,7 @@
         <v>1</v>
       </c>
       <c r="M2" s="9" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -6569,7 +6586,7 @@
         <v>0</v>
       </c>
       <c r="M3" s="9" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -6583,7 +6600,7 @@
         <v>23</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="E4" s="9">
         <v>0</v>
@@ -6622,7 +6639,7 @@
         <v>23</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="E5" s="9">
         <v>18</v>
@@ -6649,12 +6666,12 @@
         <v>0</v>
       </c>
       <c r="M5" s="9" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="6" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="B6" s="5" t="s">
         <v>22</v>
@@ -6669,7 +6686,7 @@
         <v>57</v>
       </c>
       <c r="F6" s="11">
-        <v>0.7667</v>
+        <v>0.9867</v>
       </c>
       <c r="G6" s="5">
         <v>48</v>
@@ -6713,47 +6730,47 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="B1" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
     </row>
-    <row r="2" ht="42" spans="1:2">
+    <row r="2" ht="28" spans="1:2">
       <c r="A2" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
     </row>
     <row r="4" ht="56" spans="1:2">
       <c r="A4" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
     </row>
     <row r="23" spans="1:16">

--- a/缺陷明细.xlsx
+++ b/缺陷明细.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="25600" windowHeight="11630" activeTab="1"/>
+    <workbookView windowWidth="25600" windowHeight="11630" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -12,7 +12,7 @@
     <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$W$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$W$19</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -769,46 +769,80 @@
     </r>
   </si>
   <si>
+    <t>待协调事项</t>
+  </si>
+  <si>
+    <t>&lt;p&gt;1、遗留缺陷 &lt;span style="color: #fd4f4f;"&gt;&lt;strong&gt;5 个&lt;/strong&gt;&lt;/span&gt;，其中 3 个超期 3 天未处理，2 个超期 7 天未处理，&lt;span style="color: #fd4f4f; background-color: #f8cac6;"&gt;&lt;strong&gt;开发修复效率较低。&lt;/strong&gt;&lt;/span&gt;&amp;mdash;&amp;mdash;请 PM 及时跟进。&lt;/p&gt;
+&lt;p&gt;2、&lt;strong&gt;【规则反向数据同步验证】&lt;/strong&gt;遗留问题：&lt;/p&gt;
+&lt;p style="padding-left: 40px;"&gt;1）运营指标 - 前置取数 -- 规则&lt;strong&gt;未开发 &lt;/strong&gt;&lt;/p&gt;
+&lt;p style="padding-left: 40px;"&gt;2）所有同步接口 opType:DELETE -- 删除的场景&lt;strong&gt;未验证&lt;/strong&gt;。&lt;/p&gt;
+&lt;p&gt;❗规则反馈&lt;strong&gt;【运营指标 - 前置取数同步接口】二期&lt;/strong&gt;上线 &amp;mdash;&amp;mdash;请 PM 及时跟进。&lt;/p&gt;
+&lt;p&gt;3、&lt;strong&gt;回归环境&lt;/strong&gt;多个中心的&lt;strong&gt;反向数据&lt;span style="color: #fd4f4f;"&gt;未同步&lt;/span&gt;：&lt;/strong&gt;&lt;/p&gt;
+&lt;p style="padding-left: 40px;"&gt;1）规则中心&lt;/p&gt;
+&lt;p style="padding-left: 40px;"&gt;2）产商品中心&lt;/p&gt;
+&lt;p&gt;❗导致回归验证&lt;strong&gt;不全面&lt;/strong&gt;。&amp;mdash;&amp;mdash;请 PM 及时跟进。&lt;/p&gt;
+&lt;hr /&gt;
+&lt;table style="border-collapse: collapse; width: 63.629%; height: 88px; background-color: #ecf0f1; border-color: #7E8C8D; border-style: solid;" border="1" cellspacing="0"&gt;
+&lt;tbody&gt;
+&lt;tr style="height: 44px;"&gt;
+&lt;th style="width: 19.805%; height: 44px;"&gt;开始时间&lt;/th&gt;
+&lt;th style="width: 19.805%; height: 44px;"&gt;结束时间&lt;/th&gt;
+&lt;th style="width: 11.7407%; height: 44px;"&gt;执行时长(秒)&lt;/th&gt;
+&lt;th style="width: 6.13811%; height: 44px;"&gt;用例数&lt;/th&gt;
+&lt;th style="width: 6.13811%; height: 44px;"&gt;通过数&lt;/th&gt;
+&lt;th style="width: 6.13811%; height: 44px;"&gt;失败数&lt;/th&gt;
+&lt;th style="width: 8.18414%; height: 44px;"&gt;未执行数&lt;/th&gt;
+&lt;th style="width: 8.21345%; height: 44px;"&gt;通过率&lt;/th&gt;
+&lt;/tr&gt;
+&lt;tr style="height: 44px;"&gt;
+&lt;th style="width: 19.805%; height: 44px;"&gt;2025-07-11 08:30:05&lt;/th&gt;
+&lt;th style="width: 19.805%; height: 44px;"&gt;2025-07-11 08:31:37&lt;/th&gt;
+&lt;th style="width: 11.7407%; height: 44px;"&gt;92&lt;/th&gt;
+&lt;th style="width: 6.13811%; height: 44px;"&gt;44&lt;/th&gt;
+&lt;th style="width: 6.13811%; height: 44px;"&gt;44&lt;/th&gt;
+&lt;th style="width: 6.13811%; height: 44px;"&gt;0&lt;/th&gt;
+&lt;th style="width: 8.18414%; height: 44px;"&gt;0&lt;/th&gt;
+&lt;th style="width: 8.21345%; height: 44px;"&gt;100.00%&lt;br /&gt;&lt;br /&gt;&lt;/th&gt;
+&lt;/tr&gt;
+&lt;/tbody&gt;
+&lt;/table&gt;</t>
+  </si>
+  <si>
     <t>测试进度和缺陷统计</t>
   </si>
   <si>
-    <t>待协调事项</t>
-  </si>
-  <si>
-    <t>&lt;p&gt;1、遗留缺陷&lt;strong&gt;5个&lt;/strong&gt;，其中&lt;strong&gt;3&lt;/strong&gt;&lt;strong&gt;个&lt;/strong&gt;超期&lt;strong&gt;&lt;span style="color: rgb(255, 0, 0);"&gt;3天&lt;/span&gt;&lt;/strong&gt;未处理，&lt;strong&gt;2个&lt;/strong&gt;超期&lt;span style="color: rgb(255, 0, 0);"&gt;&lt;strong&gt;7天&lt;/strong&gt;&lt;/span&gt;未处理，&lt;strong&gt;&lt;span style="color: rgb(255, 0, 0);"&gt;开发修复效率较低。&lt;/span&gt;&lt;/strong&gt;&lt;strong&gt;&lt;span style="color: rgb(255, 0, 0);"&gt;——请PM及时跟进。&lt;/span&gt;&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;2、规则反向数据同步验证遗留问题：1、运营指标-前置取数 --规则未开发 2、所有同步接口opType:DELETE-删除的场景未验证。规则反馈运营指标-前置取数同步接口二期上线&lt;span style="color: rgb(255, 0, 0);"&gt;&lt;strong&gt;——请PM及时跟进。&lt;/strong&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;3、回归环境多个中心的&lt;strong&gt;&lt;span style="color: rgb(255, 0, 0);"&gt;反向数据未同步&lt;/span&gt;&lt;/strong&gt;：&lt;/p&gt;&lt;p&gt;规则中心&lt;/p&gt;&lt;p&gt;导致&lt;strong&gt;回归验证不全面&lt;/strong&gt;。&lt;span style="color: rgb(255, 0, 0);"&gt;&lt;strong&gt;——请PM及时跟进。&lt;/strong&gt;&lt;/span&gt;&lt;/p&gt;</t>
-  </si>
-  <si>
     <t>PSOT-UI自动化建设</t>
   </si>
   <si>
-    <r>
-      <t>完成场景数15/70，自动化执行成功</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>100%</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>，下周继续推进UI自动化建设。
-测试资源投入：
-邱钰洁：本周计划完成100%
-叶怡馨：本周计划完成10%，因需求上线紧张无法投入
-陈彦均：本周计划完成100%</t>
-    </r>
+    <t>&lt;p&gt;&lt;strong&gt;完成场景数15/70，自动化执行成功80%，下周计划：继续推进。&lt;/strong&gt;&lt;/p&gt;
+&lt;ul&gt;
+&lt;li&gt;&lt;strong&gt;测试资源投入：&lt;/strong&gt;&lt;br /&gt;邱钰洁：本周计划完成100%&lt;br /&gt;叶怡馨：本周计划完成10%，&lt;strong&gt;因需求上线紧张无法投入&lt;/strong&gt;&lt;br /&gt;陈彦均：本周计划完成100%&lt;/li&gt;
+&lt;/ul&gt;
+&lt;hr /&gt;
+&lt;table style="width: 76.0781%; height: 88px;" border="1" cellspacing="0"&gt;
+&lt;tbody&gt;
+&lt;tr style="height: 44px;"&gt;
+&lt;th style="width: 12.8606%; height: 44px;"&gt;开始时间&lt;/th&gt;
+&lt;th style="width: 10.8764%; height: 44px;"&gt;结束时间&lt;/th&gt;
+&lt;th style="width: 11.75%; height: 44px;"&gt;执行时长(秒)&lt;/th&gt;
+&lt;th style="width: 9.10002%; height: 44px;"&gt;用例数&lt;/th&gt;
+&lt;th style="width: 10.6699%; height: 44px;"&gt;通开始过数&lt;/th&gt;
+&lt;th style="width: 10.2165%; height: 44px;"&gt;失败数&lt;/th&gt;
+&lt;th style="width: 8.42128%; height: 44px;"&gt;未执行数&lt;/th&gt;
+&lt;th style="width: 12.2679%; height: 44px;"&gt;通过率&lt;/th&gt;
+&lt;/tr&gt;
+&lt;tr style="height: 44px;"&gt;
+&lt;th style="width: 12.8606%; height: 44px;"&gt;2025-07-11 08:30:05&lt;/th&gt;
+&lt;th style="width: 10.8764%; height: 44px;"&gt;2025-07-11 08:31:37&lt;/th&gt;
+&lt;th style="width: 11.75%; height: 44px;"&gt;92&lt;/th&gt;
+&lt;th style="width: 9.10002%; height: 44px;"&gt;44&lt;/th&gt;
+&lt;th style="width: 10.6699%; height: 44px;"&gt;44&lt;/th&gt;
+&lt;th style="width: 10.2165%; height: 44px;"&gt;0&lt;/th&gt;
+&lt;th style="width: 8.42128%; height: 44px;"&gt;0&lt;/th&gt;
+&lt;th style="width: 12.2679%; height: 44px;"&gt;100.00%&lt;br /&gt;&lt;br /&gt;&lt;/th&gt;
+&lt;/tr&gt;
+&lt;/tbody&gt;
+&lt;/table&gt;</t>
   </si>
   <si>
     <t>下周测试计划</t>
@@ -1908,7 +1942,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:AF19"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
@@ -1997,7 +2031,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="2" ht="15" spans="1:32">
+    <row r="2" ht="15" hidden="1" spans="1:32">
       <c r="A2" s="10" t="s">
         <v>22</v>
       </c>
@@ -2149,7 +2183,7 @@
       <c r="AE3" s="20"/>
       <c r="AF3" s="20"/>
     </row>
-    <row r="4" ht="15" spans="1:32">
+    <row r="4" ht="15" hidden="1" spans="1:32">
       <c r="A4" s="10" t="s">
         <v>22</v>
       </c>
@@ -2229,7 +2263,7 @@
       <c r="AE4" s="20"/>
       <c r="AF4" s="20"/>
     </row>
-    <row r="5" ht="15" spans="1:32">
+    <row r="5" ht="15" hidden="1" spans="1:32">
       <c r="A5" s="10" t="s">
         <v>22</v>
       </c>
@@ -2309,7 +2343,7 @@
       <c r="AE5" s="20"/>
       <c r="AF5" s="20"/>
     </row>
-    <row r="6" ht="15" spans="1:32">
+    <row r="6" ht="15" hidden="1" spans="1:32">
       <c r="A6" s="10" t="s">
         <v>22</v>
       </c>
@@ -2389,7 +2423,7 @@
       <c r="AE6" s="20"/>
       <c r="AF6" s="20"/>
     </row>
-    <row r="7" ht="15" spans="1:32">
+    <row r="7" ht="15" hidden="1" spans="1:32">
       <c r="A7" s="10" t="s">
         <v>22</v>
       </c>
@@ -2467,7 +2501,7 @@
       <c r="AE7" s="20"/>
       <c r="AF7" s="20"/>
     </row>
-    <row r="8" ht="15" spans="1:32">
+    <row r="8" ht="15" hidden="1" spans="1:32">
       <c r="A8" s="10" t="s">
         <v>22</v>
       </c>
@@ -2547,7 +2581,7 @@
       <c r="AE8" s="20"/>
       <c r="AF8" s="20"/>
     </row>
-    <row r="9" ht="15" spans="1:32">
+    <row r="9" ht="15" hidden="1" spans="1:32">
       <c r="A9" s="10" t="s">
         <v>22</v>
       </c>
@@ -2627,7 +2661,7 @@
       <c r="AE9" s="20"/>
       <c r="AF9" s="20"/>
     </row>
-    <row r="10" ht="15" spans="1:32">
+    <row r="10" ht="15" hidden="1" spans="1:32">
       <c r="A10" s="10" t="s">
         <v>22</v>
       </c>
@@ -2707,7 +2741,7 @@
       <c r="AE10" s="20"/>
       <c r="AF10" s="20"/>
     </row>
-    <row r="11" ht="15" spans="1:32">
+    <row r="11" ht="15" hidden="1" spans="1:32">
       <c r="A11" s="10" t="s">
         <v>22</v>
       </c>
@@ -2787,7 +2821,7 @@
       <c r="AE11" s="20"/>
       <c r="AF11" s="20"/>
     </row>
-    <row r="12" ht="15" spans="1:32">
+    <row r="12" ht="15" hidden="1" spans="1:32">
       <c r="A12" s="10" t="s">
         <v>22</v>
       </c>
@@ -3011,7 +3045,7 @@
       <c r="AE14" s="20"/>
       <c r="AF14" s="20"/>
     </row>
-    <row r="15" ht="15" spans="1:32">
+    <row r="15" ht="15" hidden="1" spans="1:32">
       <c r="A15" s="10" t="s">
         <v>22</v>
       </c>
@@ -3091,7 +3125,7 @@
       <c r="AE15" s="20"/>
       <c r="AF15" s="20"/>
     </row>
-    <row r="16" ht="15" spans="1:32">
+    <row r="16" ht="15" hidden="1" spans="1:32">
       <c r="A16" s="10" t="s">
         <v>22</v>
       </c>
@@ -3171,7 +3205,7 @@
       <c r="AE16" s="20"/>
       <c r="AF16" s="20"/>
     </row>
-    <row r="17" ht="15" spans="1:32">
+    <row r="17" ht="15" hidden="1" spans="1:32">
       <c r="A17" s="10" t="s">
         <v>22</v>
       </c>
@@ -3251,7 +3285,7 @@
       <c r="AE17" s="20"/>
       <c r="AF17" s="20"/>
     </row>
-    <row r="18" ht="15" spans="1:32">
+    <row r="18" ht="15" hidden="1" spans="1:32">
       <c r="A18" s="10" t="s">
         <v>22</v>
       </c>
@@ -3331,7 +3365,7 @@
       <c r="AE18" s="20"/>
       <c r="AF18" s="20"/>
     </row>
-    <row r="19" ht="15" spans="1:32">
+    <row r="19" ht="15" hidden="1" spans="1:32">
       <c r="A19" s="10" t="s">
         <v>22</v>
       </c>
@@ -3410,7 +3444,12 @@
       <c r="AF19" s="20"/>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:W1" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:W19" etc:filterBottomFollowUsedRange="0">
+    <filterColumn colId="6">
+      <filters>
+        <filter val="New"/>
+      </filters>
+    </filterColumn>
     <extLst/>
   </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3769,20 +3808,20 @@
         <v>122</v>
       </c>
     </row>
-    <row r="3" spans="1:2">
+    <row r="3" ht="409" customHeight="1" spans="1:2">
       <c r="A3" t="s">
         <v>123</v>
       </c>
+      <c r="B3" s="1" t="s">
+        <v>124</v>
+      </c>
     </row>
-    <row r="4" ht="84" spans="1:2">
+    <row r="4" customFormat="1" spans="1:2">
       <c r="A4" t="s">
-        <v>124</v>
-      </c>
-      <c r="B4" s="1" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="5" ht="70" spans="1:2">
+    <row r="5" ht="409.5" spans="1:2">
       <c r="A5" t="s">
         <v>126</v>
       </c>

--- a/缺陷明细.xlsx
+++ b/缺陷明细.xlsx
@@ -769,6 +769,9 @@
     </r>
   </si>
   <si>
+    <t>测试进度和缺陷统计</t>
+  </si>
+  <si>
     <t>待协调事项</t>
   </si>
   <si>
@@ -806,9 +809,6 @@
 &lt;/tr&gt;
 &lt;/tbody&gt;
 &lt;/table&gt;</t>
-  </si>
-  <si>
-    <t>测试进度和缺陷统计</t>
   </si>
   <si>
     <t>PSOT-UI自动化建设</t>
@@ -3808,16 +3808,16 @@
         <v>122</v>
       </c>
     </row>
-    <row r="3" ht="409" customHeight="1" spans="1:2">
+    <row r="3" customFormat="1" spans="1:2">
       <c r="A3" t="s">
         <v>123</v>
       </c>
-      <c r="B3" s="1" t="s">
+    </row>
+    <row r="4" ht="409" customHeight="1" spans="1:2">
+      <c r="A4" t="s">
         <v>124</v>
       </c>
-    </row>
-    <row r="4" customFormat="1" spans="1:2">
-      <c r="A4" t="s">
+      <c r="B4" s="1" t="s">
         <v>125</v>
       </c>
     </row>

--- a/缺陷明细.xlsx
+++ b/缺陷明细.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="25600" windowHeight="11630" activeTab="2"/>
+    <workbookView windowWidth="25600" windowHeight="11630"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -12,7 +12,7 @@
     <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$W$19</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$AF$19</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -638,7 +638,7 @@
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
-      <t>，回归总进度95%。
+      <t>，回归总进度90%。
 本周新增缺陷总数</t>
     </r>
     <r>
@@ -775,7 +775,7 @@
     <t>待协调事项</t>
   </si>
   <si>
-    <t>&lt;p&gt;1、遗留缺陷 &lt;span style="color: #fd4f4f;"&gt;&lt;strong&gt;5 个&lt;/strong&gt;&lt;/span&gt;，其中 3 个超期 3 天未处理，2 个超期 7 天未处理，&lt;span style="color: #fd4f4f; background-color: #f8cac6;"&gt;&lt;strong&gt;开发修复效率较低。&lt;/strong&gt;&lt;/span&gt;&amp;mdash;&amp;mdash;请 PM 及时跟进。&lt;/p&gt;
+    <t>&lt;p&gt;1、遗留缺陷 &lt;span style="color: #fd4f4f;"&gt;&lt;strong&gt;5 个&lt;/strong&gt;&lt;/span&gt;，其中 2 个超期 3 天以上未处理&lt;span style="color: #fd4f4f; background-color: #f8cac6;"&gt;&lt;strong&gt;开发修复效率较低。&lt;/strong&gt;&lt;/span&gt;&amp;mdash;&amp;mdash;请 PM 及时跟进。&lt;/p&gt;
 &lt;p&gt;2、&lt;strong&gt;【规则反向数据同步验证】&lt;/strong&gt;遗留问题：&lt;/p&gt;
 &lt;p style="padding-left: 40px;"&gt;1）运营指标 - 前置取数 -- 规则&lt;strong&gt;未开发 &lt;/strong&gt;&lt;/p&gt;
 &lt;p style="padding-left: 40px;"&gt;2）所有同步接口 opType:DELETE -- 删除的场景&lt;strong&gt;未验证&lt;/strong&gt;。&lt;/p&gt;
@@ -2423,7 +2423,7 @@
       <c r="AE6" s="20"/>
       <c r="AF6" s="20"/>
     </row>
-    <row r="7" ht="15" hidden="1" spans="1:32">
+    <row r="7" ht="15" spans="1:32">
       <c r="A7" s="10" t="s">
         <v>22</v>
       </c>
@@ -3365,7 +3365,7 @@
       <c r="AE18" s="20"/>
       <c r="AF18" s="20"/>
     </row>
-    <row r="19" ht="15" hidden="1" spans="1:32">
+    <row r="19" ht="15" spans="1:32">
       <c r="A19" s="10" t="s">
         <v>22</v>
       </c>
@@ -3444,10 +3444,11 @@
       <c r="AF19" s="20"/>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:W19" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:AF19" etc:filterBottomFollowUsedRange="0">
     <filterColumn colId="6">
       <filters>
         <filter val="New"/>
+        <filter val="ReOpen"/>
       </filters>
     </filterColumn>
     <extLst/>
@@ -3534,7 +3535,7 @@
         <v>1</v>
       </c>
       <c r="G2" s="8">
-        <v>0.2</v>
+        <v>0.8</v>
       </c>
       <c r="H2" s="7">
         <v>4</v>
@@ -3622,7 +3623,7 @@
         <v>1</v>
       </c>
       <c r="G4" s="11">
-        <v>0.95</v>
+        <v>1</v>
       </c>
       <c r="H4" s="7">
         <v>0</v>
@@ -3750,7 +3751,8 @@
         <v>1</v>
       </c>
       <c r="G7" s="12">
-        <v>0.95</v>
+        <f>AVERAGE(G2:G6)</f>
+        <v>0.9</v>
       </c>
       <c r="H7" s="4">
         <v>18</v>

--- a/缺陷明细.xlsx
+++ b/缺陷明细.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="25600" windowHeight="11630"/>
+    <workbookView windowWidth="25600" windowHeight="11630" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -31,8 +31,12 @@
 </workbook>
 </file>
 
+<file path=xl/cellimages.xml><?xml version="1.0" encoding="utf-8"?>
+<etc:cellImages xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData"/>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="382" uniqueCount="130">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="384" uniqueCount="132">
   <si>
     <t>登记时间</t>
   </si>
@@ -590,6 +594,9 @@
   </si>
   <si>
     <t>内容</t>
+  </si>
+  <si>
+    <t>图片</t>
   </si>
   <si>
     <t>本周测试概况</t>
@@ -775,74 +782,21 @@
     <t>待协调事项</t>
   </si>
   <si>
-    <t>&lt;p&gt;1、遗留缺陷 &lt;span style="color: #fd4f4f;"&gt;&lt;strong&gt;5 个&lt;/strong&gt;&lt;/span&gt;，其中 2 个超期 3 天以上未处理&lt;span style="color: #fd4f4f; background-color: #f8cac6;"&gt;&lt;strong&gt;开发修复效率较低。&lt;/strong&gt;&lt;/span&gt;&amp;mdash;&amp;mdash;请 PM 及时跟进。&lt;/p&gt;
-&lt;p&gt;2、&lt;strong&gt;【规则反向数据同步验证】&lt;/strong&gt;遗留问题：&lt;/p&gt;
-&lt;p style="padding-left: 40px;"&gt;1）运营指标 - 前置取数 -- 规则&lt;strong&gt;未开发 &lt;/strong&gt;&lt;/p&gt;
-&lt;p style="padding-left: 40px;"&gt;2）所有同步接口 opType:DELETE -- 删除的场景&lt;strong&gt;未验证&lt;/strong&gt;。&lt;/p&gt;
-&lt;p&gt;❗规则反馈&lt;strong&gt;【运营指标 - 前置取数同步接口】二期&lt;/strong&gt;上线 &amp;mdash;&amp;mdash;请 PM 及时跟进。&lt;/p&gt;
-&lt;p&gt;3、&lt;strong&gt;回归环境&lt;/strong&gt;多个中心的&lt;strong&gt;反向数据&lt;span style="color: #fd4f4f;"&gt;未同步&lt;/span&gt;：&lt;/strong&gt;&lt;/p&gt;
-&lt;p style="padding-left: 40px;"&gt;1）规则中心&lt;/p&gt;
-&lt;p style="padding-left: 40px;"&gt;2）产商品中心&lt;/p&gt;
-&lt;p&gt;❗导致回归验证&lt;strong&gt;不全面&lt;/strong&gt;。&amp;mdash;&amp;mdash;请 PM 及时跟进。&lt;/p&gt;
-&lt;hr /&gt;
-&lt;table style="border-collapse: collapse; width: 63.629%; height: 88px; background-color: #ecf0f1; border-color: #7E8C8D; border-style: solid;" border="1" cellspacing="0"&gt;
-&lt;tbody&gt;
-&lt;tr style="height: 44px;"&gt;
-&lt;th style="width: 19.805%; height: 44px;"&gt;开始时间&lt;/th&gt;
-&lt;th style="width: 19.805%; height: 44px;"&gt;结束时间&lt;/th&gt;
-&lt;th style="width: 11.7407%; height: 44px;"&gt;执行时长(秒)&lt;/th&gt;
-&lt;th style="width: 6.13811%; height: 44px;"&gt;用例数&lt;/th&gt;
-&lt;th style="width: 6.13811%; height: 44px;"&gt;通过数&lt;/th&gt;
-&lt;th style="width: 6.13811%; height: 44px;"&gt;失败数&lt;/th&gt;
-&lt;th style="width: 8.18414%; height: 44px;"&gt;未执行数&lt;/th&gt;
-&lt;th style="width: 8.21345%; height: 44px;"&gt;通过率&lt;/th&gt;
-&lt;/tr&gt;
-&lt;tr style="height: 44px;"&gt;
-&lt;th style="width: 19.805%; height: 44px;"&gt;2025-07-11 08:30:05&lt;/th&gt;
-&lt;th style="width: 19.805%; height: 44px;"&gt;2025-07-11 08:31:37&lt;/th&gt;
-&lt;th style="width: 11.7407%; height: 44px;"&gt;92&lt;/th&gt;
-&lt;th style="width: 6.13811%; height: 44px;"&gt;44&lt;/th&gt;
-&lt;th style="width: 6.13811%; height: 44px;"&gt;44&lt;/th&gt;
-&lt;th style="width: 6.13811%; height: 44px;"&gt;0&lt;/th&gt;
-&lt;th style="width: 8.18414%; height: 44px;"&gt;0&lt;/th&gt;
-&lt;th style="width: 8.21345%; height: 44px;"&gt;100.00%&lt;br /&gt;&lt;br /&gt;&lt;/th&gt;
-&lt;/tr&gt;
-&lt;/tbody&gt;
-&lt;/table&gt;</t>
+    <t>/待协调事项文档.html</t>
   </si>
   <si>
     <t>PSOT-UI自动化建设</t>
   </si>
   <si>
-    <t>&lt;p&gt;&lt;strong&gt;完成场景数15/70，自动化执行成功80%，下周计划：继续推进。&lt;/strong&gt;&lt;/p&gt;
-&lt;ul&gt;
-&lt;li&gt;&lt;strong&gt;测试资源投入：&lt;/strong&gt;&lt;br /&gt;邱钰洁：本周计划完成100%&lt;br /&gt;叶怡馨：本周计划完成10%，&lt;strong&gt;因需求上线紧张无法投入&lt;/strong&gt;&lt;br /&gt;陈彦均：本周计划完成100%&lt;/li&gt;
-&lt;/ul&gt;
-&lt;hr /&gt;
-&lt;table style="width: 76.0781%; height: 88px;" border="1" cellspacing="0"&gt;
-&lt;tbody&gt;
-&lt;tr style="height: 44px;"&gt;
-&lt;th style="width: 12.8606%; height: 44px;"&gt;开始时间&lt;/th&gt;
-&lt;th style="width: 10.8764%; height: 44px;"&gt;结束时间&lt;/th&gt;
-&lt;th style="width: 11.75%; height: 44px;"&gt;执行时长(秒)&lt;/th&gt;
-&lt;th style="width: 9.10002%; height: 44px;"&gt;用例数&lt;/th&gt;
-&lt;th style="width: 10.6699%; height: 44px;"&gt;通开始过数&lt;/th&gt;
-&lt;th style="width: 10.2165%; height: 44px;"&gt;失败数&lt;/th&gt;
-&lt;th style="width: 8.42128%; height: 44px;"&gt;未执行数&lt;/th&gt;
-&lt;th style="width: 12.2679%; height: 44px;"&gt;通过率&lt;/th&gt;
-&lt;/tr&gt;
-&lt;tr style="height: 44px;"&gt;
-&lt;th style="width: 12.8606%; height: 44px;"&gt;2025-07-11 08:30:05&lt;/th&gt;
-&lt;th style="width: 10.8764%; height: 44px;"&gt;2025-07-11 08:31:37&lt;/th&gt;
-&lt;th style="width: 11.75%; height: 44px;"&gt;92&lt;/th&gt;
-&lt;th style="width: 9.10002%; height: 44px;"&gt;44&lt;/th&gt;
-&lt;th style="width: 10.6699%; height: 44px;"&gt;44&lt;/th&gt;
-&lt;th style="width: 10.2165%; height: 44px;"&gt;0&lt;/th&gt;
-&lt;th style="width: 8.42128%; height: 44px;"&gt;0&lt;/th&gt;
-&lt;th style="width: 12.2679%; height: 44px;"&gt;100.00%&lt;br /&gt;&lt;br /&gt;&lt;/th&gt;
-&lt;/tr&gt;
-&lt;/tbody&gt;
-&lt;/table&gt;</t>
+    <t>&lt;p&gt;完成场景数12/70，自动化执行成功100%，下周计划：继续推进。&lt;/p&gt;
+&lt;p&gt;🔔注：为加快PSOT-UI自动化建设，本周主要&lt;span style="background-color: #fef0f0; color: #fc0101;"&gt;&lt;strong&gt;推进点&lt;/strong&gt;&lt;/span&gt;为：使用&lt;strong&gt;Claude Code&lt;/strong&gt;和&lt;strong&gt;playwright MCP&lt;/strong&gt;生成产标平台&lt;strong&gt;各页面&lt;/strong&gt;的&lt;strong&gt;元素定位xpath文档&lt;/strong&gt;。&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;&amp;nbsp; 文档统计&lt;/strong&gt;（截至目前扫描）&lt;/p&gt;
+&lt;p&gt;&amp;nbsp; - 文档行数：&lt;strong&gt;850&lt;/strong&gt;行&lt;br /&gt;&amp;nbsp; - XPath元素总数：约&lt;strong&gt;497&lt;/strong&gt;个&lt;br /&gt;&amp;nbsp; - 覆盖菜单：&lt;strong&gt;6&lt;/strong&gt;大菜单模块&lt;br /&gt;&amp;nbsp; - 覆盖子页面/对话框：&lt;strong&gt;30+&lt;/strong&gt;个&lt;/p&gt;
+&lt;p&gt;--以上内容尚未整合到场景中，本周将推进&lt;strong&gt;场景的建设&lt;/strong&gt;工作。&lt;/p&gt;
+&lt;p&gt;&amp;nbsp;&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t>/UI自动化元素定位.jpg</t>
   </si>
   <si>
     <t>下周测试计划</t>
@@ -3794,49 +3748,55 @@
     <col min="3" max="3" width="45.6363636363636" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:3">
       <c r="A1" t="s">
         <v>119</v>
       </c>
       <c r="B1" t="s">
         <v>120</v>
       </c>
+      <c r="C1" t="s">
+        <v>121</v>
+      </c>
     </row>
-    <row r="2" ht="28" spans="1:2">
+    <row r="2" ht="28" spans="1:3">
       <c r="A2" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
-    <row r="3" customFormat="1" spans="1:2">
+    <row r="3" customFormat="1" spans="1:3">
       <c r="A3" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
-    <row r="4" ht="409" customHeight="1" spans="1:2">
+    <row r="4" ht="101" customHeight="1" spans="1:3">
       <c r="A4" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
-    <row r="5" ht="409.5" spans="1:2">
+    <row r="5" ht="112" spans="1:3">
       <c r="A5" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>127</v>
+        <v>128</v>
+      </c>
+      <c r="C5" t="s">
+        <v>129</v>
       </c>
     </row>
-    <row r="6" spans="1:2">
+    <row r="6" spans="1:3">
       <c r="A6" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
     </row>
     <row r="23" spans="1:16">

--- a/缺陷明细.xlsx
+++ b/缺陷明细.xlsx
@@ -327,7 +327,7 @@
     <t>&lt;p&gt;本周(迭代十三)提测功能为[ppt在线编辑]、[导入导出]、[迭代优化]、[AI反向数据剔除]，测试总进度为100%，回归总进度100%。&lt;/p&gt;
 &lt;p&gt;本周新增缺陷总数4个，已关闭2个，待修复1个，待验证0个，延期1个，重新打开0个。&lt;/p&gt;
 &lt;p&gt;迭代十四上线范围为[数据权限]、[需求版本]、[PPTIST]、[信息图需求态]、[安全扫描修复]。&lt;/p&gt;
-&lt;p&gt;&lt;strong&gt;迭代十四目前未提测&lt;/strong&gt;，开发总进度 &lt;span style="background-color: #fef0f0;"&gt;&lt;strong&gt;&lt;span style="color: #fd4f4f;border-radius:12px;padding:2px 10px;"&gt;98%&lt;/span&gt;&lt;/strong&gt;&lt;/span&gt;。&lt;/p&gt;</t>
+&lt;p&gt;&lt;strong&gt;迭代十四目前&lt;span style="color: #fd4f4f;"&gt;未提测&lt;/span&gt;&lt;/strong&gt;，开发总进度&lt;span style="background-color: #fef0f0;border-radius:12px; padding:2px 10px;"&gt;&lt;strong&gt;&lt;span style="color: #fd4f4f;"&gt;98%&lt;/span&gt;&lt;/strong&gt;&lt;/span&gt;。&lt;/p&gt;</t>
   </si>
   <si>
     <t>测试进度和缺陷统计</t>

--- a/缺陷明细.xlsx
+++ b/缺陷明细.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="25600" windowHeight="11630" activeTab="2"/>
+    <workbookView windowWidth="25600" windowHeight="12080" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -12,7 +12,7 @@
     <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$AF$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$AF$5</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="86">
   <si>
     <t>登记时间</t>
   </si>
@@ -242,6 +242,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>NL-B-174230</t>
     </r>
     <r>
@@ -349,6 +356,56 @@
   </si>
   <si>
     <t>/UI自动化场景进度.jpg</t>
+  </si>
+  <si>
+    <t>AI成效</t>
+  </si>
+  <si>
+    <t>1、如下表：
+&lt;table&gt;
+&lt;tbody&gt;
+&lt;tr&gt;
+&lt;td width="59"&gt;序号&lt;/td&gt;
+&lt;td width="129"&gt;中心&lt;/td&gt;
+&lt;td width="148"&gt;团队或个人&lt;/td&gt;
+&lt;td width="156"&gt;工具名称&lt;/td&gt;
+&lt;td width="300"&gt;Git路径&lt;/td&gt;
+&lt;td width="253"&gt;工具用途&lt;/td&gt;
+&lt;/tr&gt;
+&lt;tr&gt;
+&lt;td width="59"&gt;1&lt;/td&gt;
+&lt;td width="129"&gt;BDTC&lt;/td&gt;
+&lt;td width="148"&gt;林燊&lt;/td&gt;
+&lt;td width="156"&gt;FPA快速截图工具&lt;/td&gt;
+&lt;td width="300"&gt;无git，cvs路径QualityManage\work\TEST\BASS组\专题培训\AI课题研究\AI小工具\FAP截图工具&lt;/td&gt;
+&lt;td width="253"&gt;可根据FPA文档快速生成测试截图文档，使用快捷键进行截图自动插入对应模块，可以直接查看FPA文件；可将execl测试报告转换为对应格式的word测试报告&lt;/td&gt;
+&lt;/tr&gt;
+&lt;tr&gt;
+&lt;td width="59"&gt;2&lt;/td&gt;
+&lt;td width="129"&gt;GMTC&lt;/td&gt;
+&lt;td width="148"&gt;管志敏&lt;/td&gt;
+&lt;td width="156"&gt;宽带业务工具&lt;/td&gt;
+&lt;td width="300"&gt;http://10.1.0.163:7080/QM/CRMTC/stored-procedure-generated-data&lt;/td&gt;
+&lt;td width="253"&gt;宽带账号生成与 Oracle 数据查询的一体化 Web 应用&lt;/td&gt;
+&lt;/tr&gt;
+&lt;tr&gt;
+&lt;td width="59"&gt;3&lt;/td&gt;
+&lt;td width="129"&gt;PBTC&lt;/td&gt;
+&lt;td width="148"&gt;邱钰洁&lt;/td&gt;
+&lt;td width="156"&gt;POST质量周报生成器&lt;/td&gt;
+&lt;td width="300"&gt;&amp;nbsp;&lt;/td&gt;
+&lt;td width="253"&gt;一款面向产标项目的缺陷质量分析可视化报告生成工具。读取Excel缺陷数据，自动生成交互式HTML周报，包含多维度图表、缺陷预警、三视图切换等功能，可通过在线访问，进行日常任务跟踪和质量反馈。&lt;/td&gt;
+&lt;/tr&gt;
+&lt;tr&gt;
+&lt;td width="59"&gt;4&lt;/td&gt;
+&lt;td width="129"&gt;BDTC&lt;/td&gt;
+&lt;td width="148"&gt;廖艺棋&lt;/td&gt;
+&lt;td width="156"&gt;AI test 平台&lt;/td&gt;
+&lt;td width="300"&gt;http://10.1.0.163:7080/QM/BDTC/AI-Intelligent-Test-Production/-/tree/aiagent_test_upload?ref_type=heads&lt;/td&gt;
+&lt;td width="253"&gt;一个AI test 测试平台 ，利用大语言模型（LLM）和 RAG 技术实现从需求分析、测试用例生成、Playwright 自动化脚本生成到测试执行与结果分析的全流程智能化测试自动化。&lt;/td&gt;
+&lt;/tr&gt;
+&lt;/tbody&gt;
+&lt;/table&gt;</t>
   </si>
   <si>
     <t>下周测试计划</t>
@@ -1820,7 +1877,7 @@
       <c r="AF5" s="17"/>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:AF1" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:AF5" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2151,7 +2208,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:P23"/>
+  <dimension ref="A1:P24"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="28.2727272727273" customWidth="1"/>
@@ -2202,7 +2259,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="6" ht="28" spans="1:3">
+    <row r="6" ht="409.5" spans="1:3">
       <c r="A6" t="s">
         <v>82</v>
       </c>
@@ -2210,23 +2267,31 @@
         <v>83</v>
       </c>
     </row>
-    <row r="23" spans="1:16">
-      <c r="A23" s="2"/>
-      <c r="B23" s="2"/>
-      <c r="C23" s="2"/>
-      <c r="D23" s="2"/>
-      <c r="E23" s="2"/>
-      <c r="F23" s="2"/>
-      <c r="G23" s="2"/>
-      <c r="H23" s="2"/>
-      <c r="I23" s="2"/>
-      <c r="J23" s="2"/>
-      <c r="K23" s="2"/>
-      <c r="L23" s="2"/>
-      <c r="M23" s="2"/>
-      <c r="N23" s="2"/>
-      <c r="O23" s="2"/>
-      <c r="P23" s="2"/>
+    <row r="7" ht="28" spans="1:3">
+      <c r="A7" t="s">
+        <v>84</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="24" spans="1:16">
+      <c r="A24" s="2"/>
+      <c r="B24" s="2"/>
+      <c r="C24" s="2"/>
+      <c r="D24" s="2"/>
+      <c r="E24" s="2"/>
+      <c r="F24" s="2"/>
+      <c r="G24" s="2"/>
+      <c r="H24" s="2"/>
+      <c r="I24" s="2"/>
+      <c r="J24" s="2"/>
+      <c r="K24" s="2"/>
+      <c r="L24" s="2"/>
+      <c r="M24" s="2"/>
+      <c r="N24" s="2"/>
+      <c r="O24" s="2"/>
+      <c r="P24" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/缺陷明细.xlsx
+++ b/缺陷明细.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="84">
   <si>
     <t>登记时间</t>
   </si>
@@ -356,56 +356,6 @@
   </si>
   <si>
     <t>/UI自动化场景进度.jpg</t>
-  </si>
-  <si>
-    <t>AI成效</t>
-  </si>
-  <si>
-    <t>1、如下表：
-&lt;table&gt;
-&lt;tbody&gt;
-&lt;tr&gt;
-&lt;td width="59"&gt;序号&lt;/td&gt;
-&lt;td width="129"&gt;中心&lt;/td&gt;
-&lt;td width="148"&gt;团队或个人&lt;/td&gt;
-&lt;td width="156"&gt;工具名称&lt;/td&gt;
-&lt;td width="300"&gt;Git路径&lt;/td&gt;
-&lt;td width="253"&gt;工具用途&lt;/td&gt;
-&lt;/tr&gt;
-&lt;tr&gt;
-&lt;td width="59"&gt;1&lt;/td&gt;
-&lt;td width="129"&gt;BDTC&lt;/td&gt;
-&lt;td width="148"&gt;林燊&lt;/td&gt;
-&lt;td width="156"&gt;FPA快速截图工具&lt;/td&gt;
-&lt;td width="300"&gt;无git，cvs路径QualityManage\work\TEST\BASS组\专题培训\AI课题研究\AI小工具\FAP截图工具&lt;/td&gt;
-&lt;td width="253"&gt;可根据FPA文档快速生成测试截图文档，使用快捷键进行截图自动插入对应模块，可以直接查看FPA文件；可将execl测试报告转换为对应格式的word测试报告&lt;/td&gt;
-&lt;/tr&gt;
-&lt;tr&gt;
-&lt;td width="59"&gt;2&lt;/td&gt;
-&lt;td width="129"&gt;GMTC&lt;/td&gt;
-&lt;td width="148"&gt;管志敏&lt;/td&gt;
-&lt;td width="156"&gt;宽带业务工具&lt;/td&gt;
-&lt;td width="300"&gt;http://10.1.0.163:7080/QM/CRMTC/stored-procedure-generated-data&lt;/td&gt;
-&lt;td width="253"&gt;宽带账号生成与 Oracle 数据查询的一体化 Web 应用&lt;/td&gt;
-&lt;/tr&gt;
-&lt;tr&gt;
-&lt;td width="59"&gt;3&lt;/td&gt;
-&lt;td width="129"&gt;PBTC&lt;/td&gt;
-&lt;td width="148"&gt;邱钰洁&lt;/td&gt;
-&lt;td width="156"&gt;POST质量周报生成器&lt;/td&gt;
-&lt;td width="300"&gt;&amp;nbsp;&lt;/td&gt;
-&lt;td width="253"&gt;一款面向产标项目的缺陷质量分析可视化报告生成工具。读取Excel缺陷数据，自动生成交互式HTML周报，包含多维度图表、缺陷预警、三视图切换等功能，可通过在线访问，进行日常任务跟踪和质量反馈。&lt;/td&gt;
-&lt;/tr&gt;
-&lt;tr&gt;
-&lt;td width="59"&gt;4&lt;/td&gt;
-&lt;td width="129"&gt;BDTC&lt;/td&gt;
-&lt;td width="148"&gt;廖艺棋&lt;/td&gt;
-&lt;td width="156"&gt;AI test 平台&lt;/td&gt;
-&lt;td width="300"&gt;http://10.1.0.163:7080/QM/BDTC/AI-Intelligent-Test-Production/-/tree/aiagent_test_upload?ref_type=heads&lt;/td&gt;
-&lt;td width="253"&gt;一个AI test 测试平台 ，利用大语言模型（LLM）和 RAG 技术实现从需求分析、测试用例生成、Playwright 自动化脚本生成到测试执行与结果分析的全流程智能化测试自动化。&lt;/td&gt;
-&lt;/tr&gt;
-&lt;/tbody&gt;
-&lt;/table&gt;</t>
   </si>
   <si>
     <t>下周测试计划</t>
@@ -2208,7 +2158,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:P24"/>
+  <dimension ref="A1:P23"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="28.2727272727273" customWidth="1"/>
@@ -2259,7 +2209,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="6" ht="409.5" spans="1:3">
+    <row r="6" ht="28" spans="1:3">
       <c r="A6" t="s">
         <v>82</v>
       </c>
@@ -2267,31 +2217,23 @@
         <v>83</v>
       </c>
     </row>
-    <row r="7" ht="28" spans="1:3">
-      <c r="A7" t="s">
-        <v>84</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="24" spans="1:16">
-      <c r="A24" s="2"/>
-      <c r="B24" s="2"/>
-      <c r="C24" s="2"/>
-      <c r="D24" s="2"/>
-      <c r="E24" s="2"/>
-      <c r="F24" s="2"/>
-      <c r="G24" s="2"/>
-      <c r="H24" s="2"/>
-      <c r="I24" s="2"/>
-      <c r="J24" s="2"/>
-      <c r="K24" s="2"/>
-      <c r="L24" s="2"/>
-      <c r="M24" s="2"/>
-      <c r="N24" s="2"/>
-      <c r="O24" s="2"/>
-      <c r="P24" s="2"/>
+    <row r="23" spans="1:16">
+      <c r="A23" s="2"/>
+      <c r="B23" s="2"/>
+      <c r="C23" s="2"/>
+      <c r="D23" s="2"/>
+      <c r="E23" s="2"/>
+      <c r="F23" s="2"/>
+      <c r="G23" s="2"/>
+      <c r="H23" s="2"/>
+      <c r="I23" s="2"/>
+      <c r="J23" s="2"/>
+      <c r="K23" s="2"/>
+      <c r="L23" s="2"/>
+      <c r="M23" s="2"/>
+      <c r="N23" s="2"/>
+      <c r="O23" s="2"/>
+      <c r="P23" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
